--- a/backend/data/uploads/JIG기준정보/JIG_기준정보.xlsx
+++ b/backend/data/uploads/JIG기준정보/JIG_기준정보.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\JIG기준정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C33D55A6-01DF-44DB-BEE4-C1175804E34F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6BACEF94-E3C3-461D-B62F-7C77B32A8C96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{556B5D79-0233-4FE1-A4CC-87BFDD164AC3}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{6A2CA6F6-472E-493E-9A00-943B2F9BE4C5}"/>
   </bookViews>
   <sheets>
     <sheet name="기준정보" sheetId="1" r:id="rId1"/>
@@ -507,7 +507,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1299F51B-4EB4-4C59-A76F-A81B0B2BFAF9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBD4F87D-8E98-469D-8876-510D8548D744}">
   <dimension ref="B2:K8"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>

--- a/backend/data/uploads/JIG기준정보/JIG_기준정보.xlsx
+++ b/backend/data/uploads/JIG기준정보/JIG_기준정보.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\JIG기준정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6BACEF94-E3C3-461D-B62F-7C77B32A8C96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6152B777-2E8D-4300-AA51-6A479EF6828E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{6A2CA6F6-472E-493E-9A00-943B2F9BE4C5}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{5793A651-4C63-4B31-BDDA-594786851D54}"/>
   </bookViews>
   <sheets>
     <sheet name="기준정보" sheetId="1" r:id="rId1"/>
@@ -507,7 +507,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBD4F87D-8E98-469D-8876-510D8548D744}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA0047A-157E-4F2D-A7A6-4EB83C397490}">
   <dimension ref="B2:K8"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>

--- a/backend/data/uploads/JIG기준정보/JIG_기준정보.xlsx
+++ b/backend/data/uploads/JIG기준정보/JIG_기준정보.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\JIG기준정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6152B777-2E8D-4300-AA51-6A479EF6828E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3C151A8E-DDFE-4F5E-9767-0FD821892F96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{5793A651-4C63-4B31-BDDA-594786851D54}"/>
+    <workbookView xWindow="-30240" yWindow="8376" windowWidth="23040" windowHeight="12012" xr2:uid="{9B879E0B-C70C-488F-A8F2-974817BC542E}"/>
   </bookViews>
   <sheets>
     <sheet name="기준정보" sheetId="1" r:id="rId1"/>
@@ -507,7 +507,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA0047A-157E-4F2D-A7A6-4EB83C397490}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBA0CBBD-DA99-43FB-8615-333C7B60E977}">
   <dimension ref="B2:K8"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
